--- a/reports/e2e_test_report.xlsx
+++ b/reports/e2e_test_report.xlsx
@@ -464,7 +464,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Execution Date: 2026-06-13 21:18:48</t>
+          <t>Execution Date: 2026-06-13 21:26:17</t>
         </is>
       </c>
     </row>
